--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4088c3406efdaf2/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{6C0E7590-660F-48BC-B9EB-DD426F3E3F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A9826ED-76C9-417D-90F7-600A42650707}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B892F2-502F-467D-9722-F15FF48DDA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -649,14 +649,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>540414</v>
+        <v>507502</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>637688.52</v>
+        <v>598852.36</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+2</f>
-        <v>59543.966800000002</v>
+        <v>56048.712399999997</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B892F2-502F-467D-9722-F15FF48DDA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA34851-4D52-4543-8F8B-C138DA87E746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -649,14 +649,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>507502</v>
+        <v>681739</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>598852.36</v>
+        <v>804452.0199999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+2</f>
-        <v>56048.712399999997</v>
+        <v>74552.681799999991</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA34851-4D52-4543-8F8B-C138DA87E746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1419E71-35C8-49C1-8103-A72C4DD8E866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -665,8 +665,8 @@
         <v>1500</v>
       </c>
       <c r="F5" s="4">
-        <f>C5*D5+E5+650+2</f>
-        <v>74552.681799999991</v>
+        <f>C5*D5+E5+650+1.3</f>
+        <v>74551.981799999994</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1419E71-35C8-49C1-8103-A72C4DD8E866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A365CF7-69E2-4917-9E25-83F68774F030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A365CF7-69E2-4917-9E25-83F68774F030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF018DA8-AD7C-4422-94DD-6BE31A99D12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -648,15 +648,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
-        <v>681739</v>
-      </c>
+      <c r="A5" s="13"/>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>804452.0199999999</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +664,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>74551.981799999994</v>
+        <v>2151.3000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF018DA8-AD7C-4422-94DD-6BE31A99D12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156484A7-5212-4883-B526-DE004670C151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -648,13 +648,15 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
+      <c r="A5" s="13">
+        <v>495499</v>
+      </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>0</v>
+        <v>584688.81999999995</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -664,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>2151.3000000000002</v>
+        <v>54773.293799999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156484A7-5212-4883-B526-DE004670C151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC3B26C-3278-4E4F-BBFE-6E3FE23E90AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -649,14 +649,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>495499</v>
+        <v>576146</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>584688.81999999995</v>
+        <v>679852.27999999991</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>54773.293799999999</v>
+        <v>63338.005199999992</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC3B26C-3278-4E4F-BBFE-6E3FE23E90AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9750FAF-A83C-46CE-9CBC-CA8DBB96942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -649,14 +649,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>576146</v>
+        <v>453634</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>679852.27999999991</v>
+        <v>535288.12</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>63338.005199999992</v>
+        <v>50327.230799999998</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9750FAF-A83C-46CE-9CBC-CA8DBB96942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F339486D-6E0A-430B-A72B-9E4F574EAAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -649,14 +649,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>453634</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>535288.12</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>50327.230799999998</v>
+        <v>63787.974599999994</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F339486D-6E0A-430B-A72B-9E4F574EAAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286B90B2-D6C4-4CC4-9086-E645D8F4C2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286B90B2-D6C4-4CC4-9086-E645D8F4C2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E721B48-99B8-4F2E-AB63-693D18A5EEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -649,14 +649,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>507502</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>598852.36</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>63787.974599999994</v>
+        <v>56048.0124</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E721B48-99B8-4F2E-AB63-693D18A5EEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C74578C-AA4F-44B5-B439-B3ED08D8AB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -649,14 +649,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>507502</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>598852.36</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>56048.0124</v>
+        <v>63787.974599999994</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C74578C-AA4F-44B5-B439-B3ED08D8AB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8784F9A3-5371-4B9D-974F-311BC28612BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -55,13 +55,34 @@
   </si>
   <si>
     <t>FINANCE</t>
+  </si>
+  <si>
+    <t>FRONX SIGMA</t>
+  </si>
+  <si>
+    <t>Model/Variant</t>
+  </si>
+  <si>
+    <t>RTO</t>
+  </si>
+  <si>
+    <t>RTO (Excl HYP)</t>
+  </si>
+  <si>
+    <t>IGNIS SIGMA</t>
+  </si>
+  <si>
+    <t>IGNIS DELTA</t>
+  </si>
+  <si>
+    <t>FRONX DELTA+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,6 +129,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -221,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -257,6 +285,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -279,7 +310,83 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -290,6 +397,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C11" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A7:C11" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="0">
+      <calculatedColumnFormula>B8-1500</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -589,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -602,22 +723,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -649,14 +770,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>681739</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>804452.0199999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -666,17 +787,77 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>63787.974599999994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>74551.981799999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14">
+        <v>63788</v>
+      </c>
+      <c r="C8" s="14">
+        <f>B8-1500</f>
+        <v>62288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="14">
+        <v>74552</v>
+      </c>
+      <c r="C9" s="14">
+        <f t="shared" ref="C9:C11" si="0">B9-1500</f>
+        <v>73052</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="14">
+        <v>50327</v>
+      </c>
+      <c r="C10" s="14">
+        <f t="shared" si="0"/>
+        <v>48827</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="14">
+        <v>54773</v>
+      </c>
+      <c r="C11" s="14">
+        <f t="shared" si="0"/>
+        <v>53273</v>
+      </c>
+    </row>
     <row r="15" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -684,5 +865,8 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8784F9A3-5371-4B9D-974F-311BC28612BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A5BCBE-D06B-454A-A0A7-F1AD5ECDD3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>FRONX DELTA+</t>
+  </si>
+  <si>
+    <t>BALENO SIGMA</t>
   </si>
 </sst>
 </file>
@@ -400,8 +403,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C11" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A7:C11" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C15" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A7:C15" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
@@ -710,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -770,14 +773,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>681739</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>804452.0199999999</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -787,7 +790,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>74551.981799999994</v>
+        <v>63787.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -837,7 +840,7 @@
         <v>48827</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
@@ -849,15 +852,51 @@
         <v>53273</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="14">
+        <v>56048</v>
+      </c>
+      <c r="C12" s="14">
+        <f>B12-1500</f>
+        <v>54548</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14">
+        <f>B13-1500</f>
+        <v>-1500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14">
+        <f>B14-1500</f>
+        <v>-1500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14">
+        <f>B11-1500</f>
+        <v>53273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A5BCBE-D06B-454A-A0A7-F1AD5ECDD3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BF9095-5D2D-4AFC-8543-5DCA4A950D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -772,15 +772,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
-        <v>580383</v>
-      </c>
+      <c r="A5" s="13"/>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -790,7 +788,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>63787.974599999994</v>
+        <v>2151.3000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BF9095-5D2D-4AFC-8543-5DCA4A950D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7B0F8F-0761-406F-BD09-96AA3B31BBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>BALENO SIGMA</t>
+  </si>
+  <si>
+    <t>IGNIS APLHA</t>
   </si>
 </sst>
 </file>
@@ -252,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -308,6 +311,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -403,8 +409,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C15" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A7:C15" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A7:C16" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
@@ -713,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -772,13 +778,15 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
+      <c r="A5" s="13">
+        <v>590838</v>
+      </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>0</v>
+        <v>697188.84</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -788,7 +796,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>2151.3000000000002</v>
+        <v>64898.295599999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -806,7 +814,7 @@
       <c r="A8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="21">
         <v>63788</v>
       </c>
       <c r="C8" s="14">
@@ -818,11 +826,11 @@
       <c r="A9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="21">
         <v>74552</v>
       </c>
       <c r="C9" s="14">
-        <f t="shared" ref="C9:C11" si="0">B9-1500</f>
+        <f t="shared" ref="C9:C13" si="0">B9-1500</f>
         <v>73052</v>
       </c>
     </row>
@@ -830,7 +838,7 @@
       <c r="A10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="21">
         <v>50327</v>
       </c>
       <c r="C10" s="14">
@@ -842,7 +850,7 @@
       <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="21">
         <v>54773</v>
       </c>
       <c r="C11" s="14">
@@ -852,49 +860,52 @@
     </row>
     <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="21">
+        <v>64898</v>
+      </c>
+      <c r="C12" s="14">
+        <f t="shared" si="0"/>
+        <v>63398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B13" s="21">
         <v>56048</v>
       </c>
-      <c r="C12" s="14">
-        <f>B12-1500</f>
+      <c r="C13" s="14">
+        <f t="shared" si="0"/>
         <v>54548</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14">
-        <f>B13-1500</f>
-        <v>-1500</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
-      <c r="C14" s="14">
-        <f>B14-1500</f>
-        <v>-1500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
-      <c r="C15" s="14">
-        <f>B11-1500</f>
-        <v>53273</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
     </row>
     <row r="20" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7B0F8F-0761-406F-BD09-96AA3B31BBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C688A6-0747-43B9-8D46-F98AA614A355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>IGNIS APLHA</t>
+  </si>
+  <si>
+    <t>IGNIS ZETA</t>
   </si>
 </sst>
 </file>
@@ -294,26 +297,26 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -409,8 +412,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A7:C16" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C17" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A7:C17" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
@@ -719,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -732,22 +735,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -779,14 +782,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>590838</v>
+        <v>540414</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>697188.84</v>
+        <v>637688.52</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -796,7 +799,13 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>64898.295599999998</v>
+        <v>59543.266800000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f>-C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -814,7 +823,7 @@
       <c r="A8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="15">
         <v>63788</v>
       </c>
       <c r="C8" s="14">
@@ -826,11 +835,11 @@
       <c r="A9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="15">
         <v>74552</v>
       </c>
       <c r="C9" s="14">
-        <f t="shared" ref="C9:C13" si="0">B9-1500</f>
+        <f t="shared" ref="C9:C14" si="0">B9-1500</f>
         <v>73052</v>
       </c>
     </row>
@@ -838,7 +847,7 @@
       <c r="A10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="15">
         <v>50327</v>
       </c>
       <c r="C10" s="14">
@@ -850,7 +859,7 @@
       <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="15">
         <v>54773</v>
       </c>
       <c r="C11" s="14">
@@ -860,52 +869,64 @@
     </row>
     <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="15">
+        <v>59543</v>
+      </c>
+      <c r="C12" s="14">
+        <f>B12-1500</f>
+        <v>58043</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B13" s="15">
         <v>64898</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C13" s="14">
         <f t="shared" si="0"/>
         <v>63398</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B14" s="15">
         <v>56048</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C14" s="14">
         <f t="shared" si="0"/>
         <v>54548</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
     </row>
-    <row r="20" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
     </row>
     <row r="21" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C688A6-0747-43B9-8D46-F98AA614A355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C6576A-6B05-4340-8CEA-ABCADF2E6737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -782,14 +782,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>540414</v>
+        <v>590838</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>637688.52</v>
+        <v>697188.84</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>59543.266800000005</v>
+        <v>64898.295599999998</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C6576A-6B05-4340-8CEA-ABCADF2E6737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AEBE37-0898-42B8-AF27-11529266F2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>IGNIS ZETA</t>
+  </si>
+  <si>
+    <t>BALENO SIGMA©</t>
   </si>
 </sst>
 </file>
@@ -782,30 +785,24 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>590838</v>
+        <v>533634</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>697188.84</v>
+        <v>629688.12</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
       </c>
       <c r="E5" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>64898.295599999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <f>-C3</f>
-        <v>0</v>
+        <v>57323.230799999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -904,9 +901,16 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+      <c r="A15" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="15">
+        <v>5344</v>
+      </c>
+      <c r="C15" s="14">
+        <f>Table1[[#This Row],[RTO]]-300</f>
+        <v>5044</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="14"/>
@@ -934,6 +938,9 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C15" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AEBE37-0898-42B8-AF27-11529266F2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E27A798-F2A5-41AA-899C-2EF5A0E2FD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -785,24 +785,24 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>533634</v>
+        <v>681739</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>629688.12</v>
+        <v>804452.0199999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>57323.230799999998</v>
+        <v>74551.981799999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E27A798-F2A5-41AA-899C-2EF5A0E2FD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C765EF-9D75-443F-BBFE-ADFBAF27AE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>BALENO SIGMA©</t>
+  </si>
+  <si>
+    <t>FRONX DELTA</t>
   </si>
 </sst>
 </file>
@@ -415,8 +418,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C17" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A7:C17" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A7:C18" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
@@ -725,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -785,14 +788,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>681739</v>
+        <v>648180</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>804452.0199999999</v>
+        <v>764852.39999999991</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -802,7 +805,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>74551.981799999994</v>
+        <v>70988.015999999989</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -830,107 +833,119 @@
     </row>
     <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" s="15">
-        <v>74552</v>
+        <v>70988</v>
       </c>
       <c r="C9" s="14">
-        <f t="shared" ref="C9:C14" si="0">B9-1500</f>
-        <v>73052</v>
+        <f>B9-1500</f>
+        <v>69488</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="15">
+        <v>74552</v>
+      </c>
+      <c r="C10" s="14">
+        <f t="shared" ref="C10:C15" si="0">B10-1500</f>
+        <v>73052</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B11" s="15">
         <v>50327</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C11" s="14">
         <f t="shared" si="0"/>
         <v>48827</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B12" s="15">
         <v>54773</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C12" s="14">
         <f t="shared" si="0"/>
         <v>53273</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="15">
-        <v>59543</v>
-      </c>
-      <c r="C12" s="14">
-        <f>B12-1500</f>
-        <v>58043</v>
-      </c>
-    </row>
     <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="15">
+        <v>59543</v>
+      </c>
+      <c r="C13" s="14">
+        <f>B13-1500</f>
+        <v>58043</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B14" s="15">
         <v>64898</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C14" s="14">
         <f t="shared" si="0"/>
         <v>63398</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B15" s="15">
         <v>56048</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C15" s="14">
         <f t="shared" si="0"/>
         <v>54548</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B16" s="15">
         <v>5344</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C16" s="14">
         <f>Table1[[#This Row],[RTO]]-300</f>
         <v>5044</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
     </row>
-    <row r="21" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -939,7 +954,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C15" calculatedColumn="1"/>
+    <ignoredError sqref="C16" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C765EF-9D75-443F-BBFE-ADFBAF27AE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D57C785-1DC1-49E2-A9E1-27A5E88CF0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>FRONX DELTA</t>
+  </si>
+  <si>
+    <t>BALENO DELTA</t>
   </si>
 </sst>
 </file>
@@ -788,14 +791,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>648180</v>
+        <v>540414</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>764852.39999999991</v>
+        <v>637688.52</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -805,7 +808,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>70988.015999999989</v>
+        <v>59543.266800000005</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -928,9 +931,16 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="15">
+        <v>63338</v>
+      </c>
+      <c r="C17" s="14">
+        <f>Table1[[#This Row],[RTO]]-1500</f>
+        <v>61838</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D57C785-1DC1-49E2-A9E1-27A5E88CF0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD108D1-80F9-413F-A9AD-D5709AB3D79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD108D1-80F9-413F-A9AD-D5709AB3D79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE86BBB6-5CFD-4AA2-B52F-D2B0B2A9C236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -155,7 +155,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,6 +174,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -306,7 +312,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -790,15 +796,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
-        <v>540414</v>
-      </c>
+      <c r="A5" s="13"/>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>637688.52</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -808,7 +812,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+650+1.3</f>
-        <v>59543.266800000005</v>
+        <v>2151.3000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -822,7 +826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>7</v>
       </c>
@@ -834,7 +838,7 @@
         <v>62288</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>18</v>
       </c>
@@ -846,7 +850,7 @@
         <v>69488</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>13</v>
       </c>
@@ -858,7 +862,7 @@
         <v>73052</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>11</v>
       </c>
@@ -870,7 +874,7 @@
         <v>48827</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>12</v>
       </c>
@@ -882,7 +886,7 @@
         <v>53273</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>16</v>
       </c>
@@ -894,7 +898,7 @@
         <v>58043</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>15</v>
       </c>
@@ -906,7 +910,7 @@
         <v>63398</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>14</v>
       </c>
@@ -918,7 +922,7 @@
         <v>54548</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>17</v>
       </c>
@@ -930,7 +934,7 @@
         <v>5044</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>19</v>
       </c>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE86BBB6-5CFD-4AA2-B52F-D2B0B2A9C236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24FD45B-DCC4-4DBE-A09B-4AF0A2BCF994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -431,8 +431,8 @@
   <autoFilter ref="A7:C18" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="1">
       <calculatedColumnFormula>B8-1500</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24FD45B-DCC4-4DBE-A09B-4AF0A2BCF994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0904524F-4C7F-4FCE-9891-E54C572C8914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -431,8 +431,8 @@
   <autoFilter ref="A7:C18" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="0">
       <calculatedColumnFormula>B8-1500</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -796,13 +796,15 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
+      <c r="A5" s="13">
+        <v>768888</v>
+      </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>0</v>
+        <v>1076443.2</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -811,8 +813,8 @@
         <v>1500</v>
       </c>
       <c r="F5" s="4">
-        <f>C5*D5+E5+650+1.3</f>
-        <v>2151.3000000000002</v>
+        <f>C5*D5+E5+664+1.3</f>
+        <v>99045.187999999995</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0904524F-4C7F-4FCE-9891-E54C572C8914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752654AB-2F1F-444A-8E77-D1A081DF2191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -869,11 +869,12 @@
         <v>11</v>
       </c>
       <c r="B11" s="15">
-        <v>50327</v>
+        <f>50327+14</f>
+        <v>50341</v>
       </c>
       <c r="C11" s="14">
         <f t="shared" si="0"/>
-        <v>48827</v>
+        <v>48841</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.35">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752654AB-2F1F-444A-8E77-D1A081DF2191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B13C490-8F98-4A9C-9BDF-5BFC2A934FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -857,11 +857,12 @@
         <v>13</v>
       </c>
       <c r="B10" s="15">
-        <v>74552</v>
+        <f>74552+14</f>
+        <v>74566</v>
       </c>
       <c r="C10" s="14">
         <f t="shared" ref="C10:C15" si="0">B10-1500</f>
-        <v>73052</v>
+        <v>73066</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -918,11 +919,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="15">
-        <v>56048</v>
+        <f>56048+14</f>
+        <v>56062</v>
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>54548</v>
+        <v>54562</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="21" x14ac:dyDescent="0.35">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B13C490-8F98-4A9C-9BDF-5BFC2A934FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D71269-E74B-4E3F-BC5D-D3E197F381C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -833,11 +833,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="15">
-        <v>63788</v>
+        <f>63788+14</f>
+        <v>63802</v>
       </c>
       <c r="C8" s="14">
         <f>B8-1500</f>
-        <v>62288</v>
+        <v>62302</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -845,11 +846,12 @@
         <v>18</v>
       </c>
       <c r="B9" s="15">
-        <v>70988</v>
+        <f>70988+14</f>
+        <v>71002</v>
       </c>
       <c r="C9" s="14">
         <f>B9-1500</f>
-        <v>69488</v>
+        <v>69502</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -883,11 +885,12 @@
         <v>12</v>
       </c>
       <c r="B12" s="15">
-        <v>54773</v>
+        <f>54773+14</f>
+        <v>54787</v>
       </c>
       <c r="C12" s="14">
         <f t="shared" si="0"/>
-        <v>53273</v>
+        <v>53287</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -895,11 +898,12 @@
         <v>16</v>
       </c>
       <c r="B13" s="15">
-        <v>59543</v>
+        <f>59543+14</f>
+        <v>59557</v>
       </c>
       <c r="C13" s="14">
         <f>B13-1500</f>
-        <v>58043</v>
+        <v>58057</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -907,11 +911,12 @@
         <v>15</v>
       </c>
       <c r="B14" s="15">
-        <v>64898</v>
+        <f>64898+14</f>
+        <v>64912</v>
       </c>
       <c r="C14" s="14">
         <f t="shared" si="0"/>
-        <v>63398</v>
+        <v>63412</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -932,11 +937,12 @@
         <v>17</v>
       </c>
       <c r="B16" s="15">
-        <v>5344</v>
+        <f>5344+14</f>
+        <v>5358</v>
       </c>
       <c r="C16" s="14">
         <f>Table1[[#This Row],[RTO]]-300</f>
-        <v>5044</v>
+        <v>5058</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -944,11 +950,12 @@
         <v>19</v>
       </c>
       <c r="B17" s="15">
-        <v>63338</v>
+        <f>63338+14</f>
+        <v>63352</v>
       </c>
       <c r="C17" s="14">
         <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>61838</v>
+        <v>61852</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D71269-E74B-4E3F-BC5D-D3E197F381C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF04DBD-914D-418C-BE25-A02B28CB2BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>BALENO DELTA</t>
+  </si>
+  <si>
+    <t>BALENO ZETA</t>
   </si>
 </sst>
 </file>
@@ -797,14 +800,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>768888</v>
+        <v>652417</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1076443.2</v>
+        <v>769852.05999999994</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -814,7 +817,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>99045.187999999995</v>
+        <v>71451.98539999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -958,10 +961,17 @@
         <v>61852</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="15">
+        <v>71452</v>
+      </c>
+      <c r="C18" s="14">
+        <f>Table1[[#This Row],[RTO]]-1500</f>
+        <v>69952</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
       <c r="C22" s="12"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF04DBD-914D-418C-BE25-A02B28CB2BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FA93E3-24C0-4A5B-B5B3-ABBF2A9F17AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -800,14 +800,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>652417</v>
+        <v>540414</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>769852.05999999994</v>
+        <v>637688.52</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71451.98539999999</v>
+        <v>59557.266800000005</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -901,7 +901,6 @@
         <v>16</v>
       </c>
       <c r="B13" s="15">
-        <f>59543+14</f>
         <v>59557</v>
       </c>
       <c r="C13" s="14">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FA93E3-24C0-4A5B-B5B3-ABBF2A9F17AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BCD093-7FF9-463B-BB82-FEA8EC0E00A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
+    <workbookView xWindow="2205" yWindow="585" windowWidth="20040" windowHeight="11715" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -800,14 +800,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>540414</v>
+        <v>724112</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>637688.52</v>
+        <v>854452.15999999992</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>59557.266800000005</v>
+        <v>79065.994399999996</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BCD093-7FF9-463B-BB82-FEA8EC0E00A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1611D3-FBEB-49F3-8776-CB829096DC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="585" windowWidth="20040" windowHeight="11715" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -800,24 +800,24 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>724112</v>
+        <v>928095</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>854452.15999999992</v>
+        <v>1095152.0999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
       </c>
       <c r="E5" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>79065.994399999996</v>
+        <v>99228.988999999987</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1611D3-FBEB-49F3-8776-CB829096DC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765C2D41-9EFD-45F3-99B1-6DFAA23D0E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -800,24 +800,24 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>928095</v>
+        <v>648180</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1095152.0999999999</v>
+        <v>764852.39999999991</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>99228.988999999987</v>
+        <v>71002.015999999989</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765C2D41-9EFD-45F3-99B1-6DFAA23D0E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB5AF65-9F7D-4E31-9CA8-EAC7329A6191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -800,14 +800,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>648180</v>
+        <v>540414</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>764852.39999999991</v>
+        <v>637688.52</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71002.015999999989</v>
+        <v>59557.266800000005</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB5AF65-9F7D-4E31-9CA8-EAC7329A6191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7262DEF-E446-4DD2-9AA2-332D071FCF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -276,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -315,9 +315,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -334,6 +331,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -354,7 +357,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -369,7 +372,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -384,7 +387,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -399,7 +402,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -414,7 +417,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -430,12 +433,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C18" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
   <autoFilter ref="A7:C18" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="2">
       <calculatedColumnFormula>B8-1500</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -740,10 +743,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
@@ -753,22 +756,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -820,167 +823,195 @@
         <v>59557.266800000005</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="22">
         <f>63788+14</f>
         <v>63802</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="21">
         <f>B8-1500</f>
         <v>62302</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="22">
         <f>70988+14</f>
         <v>71002</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="21">
         <f>B9-1500</f>
         <v>69502</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="22">
         <f>74552+14</f>
         <v>74566</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="21">
         <f t="shared" ref="C10:C15" si="0">B10-1500</f>
         <v>73066</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="22">
         <f>50327+14</f>
         <v>50341</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="21">
         <f t="shared" si="0"/>
         <v>48841</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="22">
         <f>54773+14</f>
         <v>54787</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="21">
         <f t="shared" si="0"/>
         <v>53287</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="22">
         <v>59557</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="21">
         <f>B13-1500</f>
         <v>58057</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="22">
         <f>64898+14</f>
         <v>64912</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="21">
         <f t="shared" si="0"/>
         <v>63412</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="22">
         <f>56048+14</f>
         <v>56062</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="21">
         <f t="shared" si="0"/>
         <v>54562</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="22">
         <f>5344+14</f>
         <v>5358</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="21">
         <f>Table1[[#This Row],[RTO]]-300</f>
         <v>5058</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="22">
         <f>63338+14</f>
         <v>63352</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="21">
         <f>Table1[[#This Row],[RTO]]-1500</f>
         <v>61852</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="22">
         <v>71452</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="21">
         <f>Table1[[#This Row],[RTO]]-1500</f>
         <v>69952</v>
       </c>
     </row>
+    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+    </row>
     <row r="22" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C22" s="12"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
+    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -315,6 +315,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -331,12 +337,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -433,12 +433,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C18" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A7:C18" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{E9027982-C4FE-4A70-9301-79918246757A}" name="RTO (Excl HYP)" dataDxfId="0">
       <calculatedColumnFormula>B8-1500</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -756,22 +756,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -824,153 +824,153 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="16">
         <f>63788+14</f>
         <v>63802</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="15">
         <f>B8-1500</f>
         <v>62302</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="16">
         <f>70988+14</f>
         <v>71002</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="15">
         <f>B9-1500</f>
         <v>69502</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="16">
         <f>74552+14</f>
         <v>74566</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="15">
         <f t="shared" ref="C10:C15" si="0">B10-1500</f>
         <v>73066</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="16">
         <f>50327+14</f>
         <v>50341</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="15">
         <f t="shared" si="0"/>
         <v>48841</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="16">
         <f>54773+14</f>
         <v>54787</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="15">
         <f t="shared" si="0"/>
         <v>53287</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="16">
         <v>59557</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="15">
         <f>B13-1500</f>
         <v>58057</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="16">
         <f>64898+14</f>
         <v>64912</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="15">
         <f t="shared" si="0"/>
         <v>63412</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="16">
         <f>56048+14</f>
         <v>56062</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="15">
         <f t="shared" si="0"/>
         <v>54562</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="16">
         <f>5344+14</f>
         <v>5358</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="15">
         <f>Table1[[#This Row],[RTO]]-300</f>
         <v>5058</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="16">
         <f>63338+14</f>
         <v>63352</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="15">
         <f>Table1[[#This Row],[RTO]]-1500</f>
         <v>61852</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="16">
         <v>71452</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="15">
         <f>Table1[[#This Row],[RTO]]-1500</f>
         <v>69952</v>
       </c>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7262DEF-E446-4DD2-9AA2-332D071FCF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844E3B14-3230-4C33-809A-1934C976120E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -803,14 +803,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>540414</v>
+        <v>652417</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>637688.52</v>
+        <v>769852.05999999994</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>59557.266800000005</v>
+        <v>71451.98539999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844E3B14-3230-4C33-809A-1934C976120E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101E1B55-C0BD-4D09-BF89-A4670DFA6F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -803,14 +803,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>652417</v>
+        <v>507502</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>769852.05999999994</v>
+        <v>598852.36</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71451.98539999999</v>
+        <v>56062.0124</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -929,7 +929,6 @@
         <v>14</v>
       </c>
       <c r="B15" s="16">
-        <f>56048+14</f>
         <v>56062</v>
       </c>
       <c r="C15" s="15">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101E1B55-C0BD-4D09-BF89-A4670DFA6F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACDC21E-8992-401F-9240-511DF4BB9C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACDC21E-8992-401F-9240-511DF4BB9C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A381F784-BF0F-4178-8CB9-5B792A0B3CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -803,14 +803,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>507502</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>598852.36</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>56062.0124</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A381F784-BF0F-4178-8CB9-5B792A0B3CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485DE07F-F28F-4871-9B4C-6201CD14A45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -803,14 +803,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>618519</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>729852.41999999993</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>67852.017799999987</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485DE07F-F28F-4871-9B4C-6201CD14A45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A60E7B-52A9-4B5E-84F1-C447E8565347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -803,14 +803,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>618519</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>729852.41999999993</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>67852.017799999987</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A60E7B-52A9-4B5E-84F1-C447E8565347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04769E7-3D74-4BA8-BFEA-36D31FE0F8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -97,13 +97,22 @@
   </si>
   <si>
     <t>BALENO ZETA</t>
+  </si>
+  <si>
+    <t>BH MV Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTO </t>
+  </si>
+  <si>
+    <t>RTO(excl Hyp)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,8 +166,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,6 +200,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -276,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -321,6 +350,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -337,6 +375,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -750,28 +791,28 @@
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="22"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -803,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>453634</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>535288.12</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -820,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>50341.230799999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -859,8 +900,12 @@
         <f>B9-1500</f>
         <v>69502</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
@@ -872,8 +917,15 @@
         <f t="shared" ref="C10:C15" si="0">B10-1500</f>
         <v>73066</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="19">
+        <f>(C5*12.5%)/7.5+1</f>
+        <v>8922.4686666666657</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>11</v>
       </c>
@@ -885,8 +937,15 @@
         <f t="shared" si="0"/>
         <v>48841</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="21">
+        <f>F10+2164</f>
+        <v>11086.468666666666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>12</v>
       </c>
@@ -898,6 +957,7 @@
         <f t="shared" si="0"/>
         <v>53287</v>
       </c>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
@@ -1013,8 +1073,9 @@
       <c r="C25" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F2"/>
+    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04769E7-3D74-4BA8-BFEA-36D31FE0F8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD7E75B-7DFA-4325-8663-1C5CC8C3EB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>453634</v>
+        <v>681739</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>535288.12</v>
+        <v>804452.0199999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>50341.230799999998</v>
+        <v>74565.981799999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>8922.4686666666657</v>
+        <v>13408.533666666664</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>11086.468666666666</v>
+        <v>15572.533666666664</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD7E75B-7DFA-4325-8663-1C5CC8C3EB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C7F92C-0ECF-4BF1-A4AD-994AEEEC703C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>681739</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>804452.0199999999</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>74565.981799999994</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>13408.533666666664</v>
+        <v>11415.198999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>15572.533666666664</v>
+        <v>13579.198999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C7F92C-0ECF-4BF1-A4AD-994AEEEC703C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11B081D-8D1E-4A38-A2FC-FE873E21502C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>648180</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>764852.39999999991</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>71002.015999999989</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>11415.198999999999</v>
+        <v>12748.539999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13579.198999999999</v>
+        <v>14912.539999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11B081D-8D1E-4A38-A2FC-FE873E21502C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B20A02-BE64-4951-BBBA-319167B51AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>648180</v>
+        <v>1021092</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>764852.39999999991</v>
+        <v>1429528.7999999998</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71002.015999999989</v>
+        <v>130822.89199999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>12748.539999999999</v>
+        <v>23826.479999999996</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>14912.539999999999</v>
+        <v>25990.479999999996</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B20A02-BE64-4951-BBBA-319167B51AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6177D48-2152-435F-96FB-646172AA09E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>1021092</v>
+        <v>652417</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1429528.7999999998</v>
+        <v>769852.05999999994</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>130822.89199999998</v>
+        <v>71451.98539999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>23826.479999999996</v>
+        <v>12831.867666666665</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>25990.479999999996</v>
+        <v>14995.867666666665</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6177D48-2152-435F-96FB-646172AA09E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B31D19-352C-4BFE-9303-309CB3F82EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B31D19-352C-4BFE-9303-309CB3F82EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84364597-05D3-4C77-8CD1-3738BA6FC7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>652417</v>
+        <v>768888</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>769852.05999999994</v>
+        <v>1076443.2</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71451.98539999999</v>
+        <v>99045.187999999995</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>12831.867666666665</v>
+        <v>17941.719999999998</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>14995.867666666665</v>
+        <v>20105.719999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84364597-05D3-4C77-8CD1-3738BA6FC7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610A6EEE-0506-4349-8117-193CF7B5E65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>768888</v>
+        <v>1019959</v>
       </c>
       <c r="B5" s="1">
         <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1076443.2</v>
+        <v>1427942.5999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>99045.187999999995</v>
+        <v>130680.13399999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>17941.719999999998</v>
+        <v>23800.043333333331</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>20105.719999999998</v>
+        <v>25964.043333333331</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610A6EEE-0506-4349-8117-193CF7B5E65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DFD5E7-8402-430C-8196-8D126F9DB74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DFD5E7-8402-430C-8196-8D126F9DB74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A334ACA-A571-4E2C-8873-6B4628FA4772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>1019959</v>
+        <v>618519</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1427942.5999999999</v>
+        <v>729852.41999999993</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>130680.13399999999</v>
+        <v>67852.017799999987</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>23800.043333333331</v>
+        <v>12165.206999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>25964.043333333331</v>
+        <v>14329.206999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A334ACA-A571-4E2C-8873-6B4628FA4772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7401C7C-5BEC-44EC-9D0A-E8530B6CF2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">RTO </t>
   </si>
   <si>
-    <t>RTO(excl Hyp)</t>
+    <t>RTO(Incl Hyp)</t>
   </si>
 </sst>
 </file>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>618519</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>729852.41999999993</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>67852.017799999987</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>12165.206999999999</v>
+        <v>11415.198999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>14329.206999999999</v>
+        <v>13579.198999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7401C7C-5BEC-44EC-9D0A-E8530B6CF2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD8E597-56FA-43D4-AEC4-6ADFD8445F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>685977</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>809452.86</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>75016.057400000005</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -910,19 +910,18 @@
         <v>13</v>
       </c>
       <c r="B10" s="16">
-        <f>74552+14</f>
-        <v>74566</v>
+        <v>75016</v>
       </c>
       <c r="C10" s="15">
         <f t="shared" ref="C10:C15" si="0">B10-1500</f>
-        <v>73066</v>
+        <v>73516</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>11415.198999999999</v>
+        <v>13491.880999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +941,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13579.198999999999</v>
+        <v>15655.880999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD8E597-56FA-43D4-AEC4-6ADFD8445F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0312668A-F52F-472E-9822-3E11FD4012E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>685977</v>
+        <v>507502</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>809452.86</v>
+        <v>598852.36</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>75016.057400000005</v>
+        <v>56062.0124</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -921,7 +921,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>13491.880999999999</v>
+        <v>9981.8726666666662</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -941,7 +941,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>15655.880999999999</v>
+        <v>12145.872666666666</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0312668A-F52F-472E-9822-3E11FD4012E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D678FFEE-966B-4841-8FEE-222A9DA7A244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -844,14 +844,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>507502</v>
+        <v>992174</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>598852.36</v>
+        <v>1389043.5999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>56062.0124</v>
+        <v>127179.22399999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -921,7 +921,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>9981.8726666666662</v>
+        <v>23151.726666666666</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -941,7 +941,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>12145.872666666666</v>
+        <v>25315.726666666666</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D678FFEE-966B-4841-8FEE-222A9DA7A244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F758E86-D57E-4FE8-A9C6-8629ED0795D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>RTO(Incl Hyp)</t>
+  </si>
+  <si>
+    <t>GV SIGMA</t>
   </si>
 </sst>
 </file>
@@ -474,8 +477,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A7:C18" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C19" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A7:C19" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
@@ -784,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -844,14 +847,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>992174</v>
+        <v>547527</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1389043.5999999999</v>
+        <v>646081.86</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -861,7 +864,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>127179.22399999999</v>
+        <v>60312.667399999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -893,12 +896,11 @@
         <v>18</v>
       </c>
       <c r="B9" s="16">
-        <f>70988+14</f>
-        <v>71002</v>
+        <v>71452</v>
       </c>
       <c r="C9" s="15">
         <f>B9-1500</f>
-        <v>69502</v>
+        <v>69952</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>21</v>
@@ -921,7 +923,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*12.5%)/7.5+1</f>
-        <v>23151.726666666666</v>
+        <v>10769.030999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -941,7 +943,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>25315.726666666666</v>
+        <v>12933.030999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1007,6 +1009,9 @@
         <f>Table1[[#This Row],[RTO]]-300</f>
         <v>5058</v>
       </c>
+      <c r="F16">
+        <v>632183</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
@@ -1033,10 +1038,17 @@
         <v>69952</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+    <row r="19" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="15">
+        <v>99045</v>
+      </c>
+      <c r="C19" s="15">
+        <f>Table1[[#This Row],[RTO]]-1500</f>
+        <v>97545</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="14"/>
@@ -1048,18 +1060,18 @@
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
     </row>
-    <row r="22" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="14"/>
@@ -1070,6 +1082,11 @@
       <c r="A25" s="14"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F758E86-D57E-4FE8-A9C6-8629ED0795D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5887C5-22E8-4BD0-9CA6-171AAC1BCAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>GV SIGMA</t>
+  </si>
+  <si>
+    <t>TAX(%)</t>
   </si>
 </sst>
 </file>
@@ -178,7 +181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +215,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -308,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -362,6 +371,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,22 +813,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -847,14 +860,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>547527</v>
+        <v>768888</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>646081.86</v>
+        <v>1076443.2</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -864,7 +877,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>60312.667399999998</v>
+        <v>99045.187999999995</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -890,8 +903,12 @@
         <f>B8-1500</f>
         <v>62302</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="30"/>
+    </row>
+    <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>18</v>
       </c>
@@ -902,10 +919,12 @@
         <f>B9-1500</f>
         <v>69952</v>
       </c>
-      <c r="E9" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="28"/>
+      <c r="E9" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="23">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
@@ -922,8 +941,8 @@
         <v>22</v>
       </c>
       <c r="F10" s="19">
-        <f>(C5*12.5%)/7.5+1</f>
-        <v>10769.030999999999</v>
+        <f>(C5*F9%)/7.5+1</f>
+        <v>14353.576000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -943,7 +962,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>12933.030999999999</v>
+        <v>16517.576000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1008,9 +1027,6 @@
       <c r="C16" s="15">
         <f>Table1[[#This Row],[RTO]]-300</f>
         <v>5058</v>
-      </c>
-      <c r="F16">
-        <v>632183</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1091,7 +1107,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F2"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5887C5-22E8-4BD0-9CA6-171AAC1BCAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C7CB4B-A461-43C2-B1E3-FF74CDB74B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -860,14 +860,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>768888</v>
+        <v>652417</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1076443.2</v>
+        <v>769852.05999999994</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>99045.187999999995</v>
+        <v>71451.98539999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -942,7 +942,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>14353.576000000001</v>
+        <v>10265.694133333333</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>16517.576000000001</v>
+        <v>12429.694133333333</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C7CB4B-A461-43C2-B1E3-FF74CDB74B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A335469A-44DD-444F-A082-55AC5DB64CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -860,14 +860,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>652417</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>769852.05999999994</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71451.98539999999</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -942,7 +942,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>10265.694133333333</v>
+        <v>9132.3592000000008</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>12429.694133333333</v>
+        <v>11296.359200000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A335469A-44DD-444F-A082-55AC5DB64CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91BE5CE-FA55-4829-9819-BCBFA25DF092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -860,14 +860,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>507502</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>598852.36</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>56062.0124</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -942,7 +942,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>9132.3592000000008</v>
+        <v>7985.6981333333342</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>11296.359200000001</v>
+        <v>10149.698133333335</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91BE5CE-FA55-4829-9819-BCBFA25DF092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0541D6A-054F-4D63-A68B-437A42746EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -860,14 +860,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>507502</v>
+        <v>728350</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>598852.36</v>
+        <v>859453</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>56062.0124</v>
+        <v>79516.070000000007</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -942,7 +942,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>7985.6981333333342</v>
+        <v>11460.373333333333</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>10149.698133333335</v>
+        <v>13624.373333333333</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0541D6A-054F-4D63-A68B-437A42746EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0E9C8B-3D7E-4FF0-9B1A-AF151BBC82E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>TAX(%)</t>
+  </si>
+  <si>
+    <t>GV DELTA</t>
   </si>
 </sst>
 </file>
@@ -490,8 +493,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C19" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A7:C19" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}" name="Table1" displayName="Table1" ref="A7:C21" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A7:C21" xr:uid="{26E5FF5E-D675-4110-8AE2-0D63A21A8B82}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E22E293B-5A23-4541-94D8-9971A1221DF9}" name="Model/Variant" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{DEB0A180-7264-4B5F-B7A3-CD607567D8CE}" name="RTO" dataDxfId="1"/>
@@ -860,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>728350</v>
+        <v>507502</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>859453</v>
+        <v>598852.36</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -877,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>79516.070000000007</v>
+        <v>56062.0124</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -923,7 +926,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="23">
-        <v>10</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>11460.373333333333</v>
+        <v>9981.8726666666662</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -962,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13624.373333333333</v>
+        <v>12145.872666666666</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1058,7 +1061,7 @@
       <c r="A19" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="16">
         <v>99045</v>
       </c>
       <c r="C19" s="15">
@@ -1066,15 +1069,25 @@
         <v>97545</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="16">
+        <v>111033</v>
+      </c>
+      <c r="C20" s="15">
+        <f t="shared" ref="C20:C21" si="1">B20-1500</f>
+        <v>109533</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="15">
+        <f t="shared" si="1"/>
+        <v>-1500</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0E9C8B-3D7E-4FF0-9B1A-AF151BBC82E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D03691-5154-4B40-8AAF-769549C49A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>507502</v>
+        <v>728350</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>598852.36</v>
+        <v>859453</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>56062.0124</v>
+        <v>79516.070000000007</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>9981.8726666666662</v>
+        <v>14325.216666666667</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>12145.872666666666</v>
+        <v>16489.216666666667</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D03691-5154-4B40-8AAF-769549C49A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2022254-B69E-4383-BDEB-48F663002D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>728350</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>859453</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>79516.070000000007</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>14325.216666666667</v>
+        <v>11415.198999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>16489.216666666667</v>
+        <v>13579.198999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2022254-B69E-4383-BDEB-48F663002D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD31320-EBB9-45BE-B430-49DB15701F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>864031</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>1209643.3999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>111033.20599999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>11415.198999999999</v>
+        <v>20161.723333333332</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13579.198999999999</v>
+        <v>22325.723333333332</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD31320-EBB9-45BE-B430-49DB15701F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7A6410-A9F4-444D-84C2-B7F12AE40793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>864031</v>
+        <v>652417</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1209643.3999999999</v>
+        <v>769852.05999999994</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>111033.20599999999</v>
+        <v>71451.98539999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>20161.723333333332</v>
+        <v>12831.867666666665</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>22325.723333333332</v>
+        <v>14995.867666666665</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7A6410-A9F4-444D-84C2-B7F12AE40793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7F8B84-C66C-4871-882E-2CFA4920EF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>652417</v>
+        <v>656655</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>769852.05999999994</v>
+        <v>774852.89999999991</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71451.98539999999</v>
+        <v>71902.060999999987</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>12831.867666666665</v>
+        <v>12915.214999999998</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>14995.867666666665</v>
+        <v>15079.214999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1050,11 +1050,11 @@
         <v>20</v>
       </c>
       <c r="B18" s="16">
-        <v>71452</v>
+        <v>71902</v>
       </c>
       <c r="C18" s="15">
         <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>69952</v>
+        <v>70402</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7F8B84-C66C-4871-882E-2CFA4920EF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D2B9E7-9750-4B3A-B738-1B8450585DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>656655</v>
+        <v>992174</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>774852.89999999991</v>
+        <v>1389043.5999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71902.060999999987</v>
+        <v>127179.22399999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>12915.214999999998</v>
+        <v>23151.726666666666</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>15079.214999999998</v>
+        <v>25315.726666666666</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D2B9E7-9750-4B3A-B738-1B8450585DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF6D2D9-EE1B-4414-BBBD-D5B3DBACB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>992174</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1389043.5999999999</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>127179.22399999999</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>23151.726666666666</v>
+        <v>11415.198999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>25315.726666666666</v>
+        <v>13579.198999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1037,12 +1037,11 @@
         <v>19</v>
       </c>
       <c r="B17" s="16">
-        <f>63338+14</f>
-        <v>63352</v>
+        <v>63802</v>
       </c>
       <c r="C17" s="15">
         <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>61852</v>
+        <v>62302</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF6D2D9-EE1B-4414-BBBD-D5B3DBACB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635E8141-8767-4E30-81E3-5E9EB3F8BADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>652417</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>769852.05999999994</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>71451.98539999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>11415.198999999999</v>
+        <v>12831.867666666665</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13579.198999999999</v>
+        <v>14995.867666666665</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635E8141-8767-4E30-81E3-5E9EB3F8BADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6F0B8A-BB90-4CDE-BE95-AB72ED725B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>652417</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>769852.05999999994</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71451.98539999999</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>12831.867666666665</v>
+        <v>11415.198999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>14995.867666666665</v>
+        <v>13579.198999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6F0B8A-BB90-4CDE-BE95-AB72ED725B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4153F8D8-A40C-4CE7-82AD-737C8CE8822F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>864031</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>1209643.3999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>111033.20599999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>11415.198999999999</v>
+        <v>20161.723333333332</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13579.198999999999</v>
+        <v>22325.723333333332</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4153F8D8-A40C-4CE7-82AD-737C8CE8822F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D9FB5A-7607-4A74-BE37-213911DACFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>864031</v>
+        <v>622756</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1209643.3999999999</v>
+        <v>734852.08</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>111033.20599999999</v>
+        <v>68301.987200000003</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>20161.723333333332</v>
+        <v>12248.534666666666</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>22325.723333333332</v>
+        <v>14412.534666666666</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D9FB5A-7607-4A74-BE37-213911DACFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68BB7C5-1B8A-4C16-BDC1-EE23650008A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>622756</v>
+        <v>864031</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>734852.08</v>
+        <v>1209643.3999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>68301.987200000003</v>
+        <v>111033.20599999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>12248.534666666666</v>
+        <v>20161.723333333332</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>14412.534666666666</v>
+        <v>22325.723333333332</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68BB7C5-1B8A-4C16-BDC1-EE23650008A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABD5601-CE8C-4826-A59B-7A2463F58AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>864031</v>
+        <v>652417</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1209643.3999999999</v>
+        <v>769852.05999999994</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>111033.20599999999</v>
+        <v>71451.98539999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>20161.723333333332</v>
+        <v>12831.867666666665</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>22325.723333333332</v>
+        <v>14995.867666666665</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABD5601-CE8C-4826-A59B-7A2463F58AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA56824-4798-4171-809C-BF01A2C8EF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>652417</v>
+        <v>822756</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>769852.05999999994</v>
+        <v>970852.08</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71451.98539999999</v>
+        <v>89541.987199999989</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>12831.867666666665</v>
+        <v>16181.867999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>14995.867666666665</v>
+        <v>18345.867999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA56824-4798-4171-809C-BF01A2C8EF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE182F88-B171-4A5E-9FA6-FB6172A60F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>822756</v>
+        <v>992174</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>970852.08</v>
+        <v>1389043.5999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>89541.987199999989</v>
+        <v>127179.22399999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>16181.867999999999</v>
+        <v>23151.726666666666</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>18345.867999999999</v>
+        <v>25315.726666666666</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE182F88-B171-4A5E-9FA6-FB6172A60F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0F66F9-F469-42D3-95A0-6A92FEF4E675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>992174</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1389043.5999999999</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>127179.22399999999</v>
+        <v>63801.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>23151.726666666666</v>
+        <v>11415.198999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>25315.726666666666</v>
+        <v>13579.198999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0F66F9-F469-42D3-95A0-6A92FEF4E675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC89C33-A143-45B7-AD4F-8A2F832F317B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>586739</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>684851.94</v>
+        <v>692352.02</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>63801.974599999994</v>
+        <v>64476.981800000001</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>11415.198999999999</v>
+        <v>11540.200333333334</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13579.198999999999</v>
+        <v>13704.200333333334</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1037,11 +1037,11 @@
         <v>19</v>
       </c>
       <c r="B17" s="16">
-        <v>63802</v>
+        <v>64477</v>
       </c>
       <c r="C17" s="15">
         <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>62302</v>
+        <v>62977</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC89C33-A143-45B7-AD4F-8A2F832F317B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC176635-EFF6-4451-A211-1F6EB78A6A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>586739</v>
+        <v>656655</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>692352.02</v>
+        <v>774852.89999999991</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>64476.981800000001</v>
+        <v>71902.060999999987</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -916,11 +916,11 @@
         <v>18</v>
       </c>
       <c r="B9" s="16">
-        <v>71452</v>
+        <v>71902</v>
       </c>
       <c r="C9" s="15">
         <f>B9-1500</f>
-        <v>69952</v>
+        <v>70402</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>25</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>11540.200333333334</v>
+        <v>12915.214999999998</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13704.200333333334</v>
+        <v>15079.214999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC176635-EFF6-4451-A211-1F6EB78A6A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4743373-32B3-45CB-A639-A333044C9A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -863,14 +863,13 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>656655</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
-        <f>A5*(1+B5)</f>
-        <v>774852.89999999991</v>
+        <v>980000</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +879,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71902.060999999987</v>
+        <v>90365.3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -926,7 +925,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="23">
-        <v>12.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -945,7 +944,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>12915.214999999998</v>
+        <v>13067.666666666666</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +964,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>15079.214999999998</v>
+        <v>15231.666666666666</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1037,11 +1036,11 @@
         <v>19</v>
       </c>
       <c r="B17" s="16">
-        <v>64477</v>
+        <v>63802</v>
       </c>
       <c r="C17" s="15">
         <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>62977</v>
+        <v>62302</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4743373-32B3-45CB-A639-A333044C9A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25185604-C3AE-4041-A5BA-2455A4E381B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -813,6 +813,7 @@
     <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -863,13 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>690214</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
-        <v>980000</v>
+        <f>A5*(1+B5)</f>
+        <v>814452.5199999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -879,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>90365.3</v>
+        <v>75466.026799999992</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,18 +935,18 @@
         <v>13</v>
       </c>
       <c r="B10" s="16">
-        <v>75016</v>
+        <v>75466</v>
       </c>
       <c r="C10" s="15">
         <f t="shared" ref="C10:C15" si="0">B10-1500</f>
-        <v>73516</v>
+        <v>73966</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>13067.666666666666</v>
+        <v>10860.366933333333</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -964,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>15231.666666666666</v>
+        <v>13024.366933333333</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25185604-C3AE-4041-A5BA-2455A4E381B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD353E5E-1C79-4C20-A2B1-5FEEE04A9082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD353E5E-1C79-4C20-A2B1-5FEEE04A9082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935AA81B-C9DD-4F80-B3F8-1F27B3E17B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>690214</v>
+        <v>992174</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>814452.5199999999</v>
+        <v>1389043.5999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>75466.026799999992</v>
+        <v>127179.22399999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>10860.366933333333</v>
+        <v>18521.581333333332</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13024.366933333333</v>
+        <v>20685.581333333332</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935AA81B-C9DD-4F80-B3F8-1F27B3E17B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6464759-32CC-49C7-897A-37FC0D05FC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>992174</v>
+        <v>961449</v>
       </c>
       <c r="B5" s="1">
         <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1389043.5999999999</v>
+        <v>1346028.5999999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>127179.22399999999</v>
+        <v>123307.87399999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>18521.581333333332</v>
+        <v>17948.047999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>20685.581333333332</v>
+        <v>20112.047999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6464759-32CC-49C7-897A-37FC0D05FC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B484231-3A32-4BDD-A818-BCBD8AA08F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>961449</v>
+        <v>690214</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>1346028.5999999999</v>
+        <v>814452.5199999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>123307.87399999998</v>
+        <v>75466.026799999992</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>17948.047999999999</v>
+        <v>10860.366933333333</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>20112.047999999999</v>
+        <v>13024.366933333333</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B484231-3A32-4BDD-A818-BCBD8AA08F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4A9090-D80E-4FC6-8249-2ACC24178E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>690214</v>
+        <v>507502</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5*(1+B5)</f>
-        <v>814452.5199999999</v>
+        <v>598852.36</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>75466.026799999992</v>
+        <v>56062.0124</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>(C5*F9%)/7.5+1</f>
-        <v>10860.366933333333</v>
+        <v>7985.6981333333342</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+2164</f>
-        <v>13024.366933333333</v>
+        <v>10149.698133333335</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4A9090-D80E-4FC6-8249-2ACC24178E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722F4224-5DB4-4B03-A4F6-737F5F5DC4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,13 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>507502</v>
+        <v>833766</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
-        <f>A5*(1+B5)</f>
-        <v>598852.36</v>
+        <v>962286</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +880,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>56062.0124</v>
+        <v>88771.04</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,8 +944,8 @@
         <v>22</v>
       </c>
       <c r="F10" s="19">
-        <f>(C5*F9%)/7.5+1</f>
-        <v>7985.6981333333342</v>
+        <f>((C5*F9%)/7.5+1)+664</f>
+        <v>13495.480000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,8 +964,8 @@
         <v>23</v>
       </c>
       <c r="F11" s="21">
-        <f>F10+2164</f>
-        <v>10149.698133333335</v>
+        <f>F10+1500</f>
+        <v>14995.480000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722F4224-5DB4-4B03-A4F6-737F5F5DC4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C41EB6F-5075-4D9D-A92C-AA6B270C5AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,13 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>833766</v>
+        <v>822756</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
-        <v>962286</v>
+        <f>A5+(A5*B5)</f>
+        <v>970852.08</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -880,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>88771.04</v>
+        <v>89541.987199999989</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -945,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>13495.480000000001</v>
+        <v>13609.6944</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>14995.480000000001</v>
+        <v>15109.6944</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C41EB6F-5075-4D9D-A92C-AA6B270C5AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21661B8-E405-4CF4-81D5-61630F87CAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>822756</v>
+        <v>768888</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>970852.08</v>
+        <v>1076443.2</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>89541.987199999989</v>
+        <v>99045.187999999995</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>13609.6944</v>
+        <v>15017.576000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>15109.6944</v>
+        <v>16517.576000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21661B8-E405-4CF4-81D5-61630F87CAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A6CD18-CC5F-4D2B-A537-4BB00FF54024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>768888</v>
+        <v>656655</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1076443.2</v>
+        <v>774852.9</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>99045.187999999995</v>
+        <v>71902.061000000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>15017.576000000001</v>
+        <v>10996.372000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>16517.576000000001</v>
+        <v>12496.372000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
